--- a/nemNguyxn Altium Library.xlsx
+++ b/nemNguyxn Altium Library.xlsx
@@ -2,21 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\nemNguyxn Altium Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F18D29A9-0FC4-4374-AC51-B3E839F84F6F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9288EE17-9EF0-4179-8052-90AAD434EF15}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{48E472BD-29E7-4696-BAF4-9A71FEFB4210}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="792" activeTab="2" xr2:uid="{48E472BD-29E7-4696-BAF4-9A71FEFB4210}"/>
   </bookViews>
   <sheets>
-    <sheet name="Capacitors" sheetId="1" r:id="rId1"/>
-    <sheet name="Resistors" sheetId="2" r:id="rId2"/>
-    <sheet name="Inductors" sheetId="3" r:id="rId3"/>
+    <sheet name="Capacitors - MLCC" sheetId="1" r:id="rId1"/>
+    <sheet name="Capacitors - TANT" sheetId="6" r:id="rId2"/>
+    <sheet name="Capacitors - ALU" sheetId="7" r:id="rId3"/>
     <sheet name="Connectors" sheetId="4" r:id="rId4"/>
+    <sheet name="Resistors" sheetId="2" r:id="rId5"/>
+    <sheet name="Inductors" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="11">
   <si>
     <t>DatabaseID</t>
   </si>
@@ -90,7 +92,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -98,24 +100,848 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="48">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -126,6 +952,66 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E978C71F-A41E-43CE-A220-B2050F36ACBD}" name="Table2" displayName="Table2" ref="A1:K1048576" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26" headerRowBorderDxfId="46" tableBorderDxfId="47" totalsRowBorderDxfId="45">
+  <autoFilter ref="A1:K1048576" xr:uid="{66998175-B102-4776-A50E-F63953463B9A}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{D053E276-1DC1-410A-89A7-0A308FA395E7}" name="DatabaseID" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{3D0743B8-4ED9-4DD5-90BD-9A5D36CF1E57}" name="Part Number" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{44837010-7A95-4B7A-AC92-B1AEDFDB4395}" name="Manufacturer" dataDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{9A8473E6-0608-4B08-9C01-31AA1D97045A}" name="Description" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{EF657F5B-B649-4F0E-B341-F87792D4634F}" name="Type" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{63B397D1-B9AF-4728-9D7C-B26B5936532F}" name="Value" dataDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{DBA5C301-A0C3-4AB9-B38F-2528D982DD51}" name="Tolerance" dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{662E95A4-09C3-4BFB-A037-8AB764D38C92}" name="Voltage Rating" dataDxfId="31"/>
+    <tableColumn id="9" xr3:uid="{E1FADA70-2281-4E8C-AD98-7321030D7867}" name="Package" dataDxfId="30"/>
+    <tableColumn id="10" xr3:uid="{E422F18C-9AAE-4FFC-8AD1-55847642433D}" name="Library Ref" dataDxfId="29"/>
+    <tableColumn id="11" xr3:uid="{05751D01-7852-4B71-8680-0E34D82D6809}" name="Footprint Ref" dataDxfId="28"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{613EA8BF-6FD5-4826-94E3-6C0A015B46ED}" name="Table24" displayName="Table24" ref="A1:K1048576" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" headerRowBorderDxfId="43" tableBorderDxfId="44" totalsRowBorderDxfId="42">
+  <autoFilter ref="A1:K1048576" xr:uid="{66998175-B102-4776-A50E-F63953463B9A}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{ABAD5B74-FBBF-4037-88B1-46B590217F8C}" name="DatabaseID" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{B357D2EB-5D65-4E54-8A2B-E575E5800D90}" name="Part Number" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{3037DE1D-4ED1-4709-B134-407F859F9709}" name="Manufacturer" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{6D5344AF-E9E5-4873-A6B9-AD21BFD38674}" name="Description" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{92396102-04A0-484E-8F33-D82E15D7FEB3}" name="Type" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{041BA87B-9138-4EEF-9E60-F8785194984B}" name="Value" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{D14B40F2-7BEE-43AB-9D7A-96001B6E8891}" name="Tolerance" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{E9C8F92E-1AB1-4BBF-8BDC-82C467938516}" name="Voltage Rating" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{78550022-E67D-4FA4-AE8C-0AE24BC02009}" name="Package" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{88338EC5-E16E-4603-85E4-C6BAC0B393D3}" name="Library Ref" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{74DA26E8-9EBA-4054-B48F-A6FA2F23581E}" name="Footprint Ref" dataDxfId="15"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{958776BD-29AD-40C3-AF4E-7B69DC8A8480}" name="Table245" displayName="Table245" ref="A1:K1048576" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="40" tableBorderDxfId="41" totalsRowBorderDxfId="39">
+  <autoFilter ref="A1:K1048576" xr:uid="{66998175-B102-4776-A50E-F63953463B9A}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{578EF4B6-1205-400A-AB04-BCC621817317}" name="DatabaseID" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{C03DC7B0-7FDB-4F9E-82FA-5B3B586BC44D}" name="Part Number" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{FE154028-2653-4796-A792-FF59166BD7B5}" name="Manufacturer" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{B0EF08C2-19D4-4ABF-85D3-776528F97E7B}" name="Description" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{650416EB-DF25-4AFA-9167-F1BEEE0E2ED1}" name="Type" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{390CB8A7-5EBB-48C9-8F91-40F6028729C0}" name="Value" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{AB722699-5B86-4B84-B4A0-C1E9991BF7AA}" name="Tolerance" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{5AF4F9CC-95C5-4951-A11B-4C55400E4486}" name="Voltage Rating" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{46E371D3-ED90-4CBF-8B90-D8EF019119FD}" name="Package" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{FE782A35-5F6B-4781-A345-33D3D7F66887}" name="Library Ref" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{07C3FA81-E9DD-4BF5-95C8-98467E814AC5}" name="Footprint Ref" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -425,59 +1311,181 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{716C64B8-3C3E-45CF-9DEE-95D0B4129A03}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="25.42578125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="74.140625" style="2" customWidth="1"/>
-    <col min="5" max="11" width="18.5703125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="74.140625" style="3" customWidth="1"/>
+    <col min="5" max="10" width="18.5703125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{636BF1F5-4643-44AA-8DF3-C9A428559F7E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC54753A-31BD-42F0-9AD1-23F915108F99}">
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.140625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="74.140625" style="3" customWidth="1"/>
+    <col min="5" max="10" width="18.5703125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" style="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{325D68EF-930E-4886-9181-27DD5105C3DE}">
+  <sheetPr codeName="Sheet6"/>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.140625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="74.140625" style="3" customWidth="1"/>
+    <col min="5" max="10" width="18.5703125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" style="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{460E9E0E-7E87-4347-8838-8149F54F8486}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -485,8 +1493,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8757DF19-A5AC-4F46-B626-CB1B3F0DFD6C}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{636BF1F5-4643-44AA-8DF3-C9A428559F7E}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -494,8 +1503,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{460E9E0E-7E87-4347-8838-8149F54F8486}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8757DF19-A5AC-4F46-B626-CB1B3F0DFD6C}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/nemNguyxn Altium Library.xlsx
+++ b/nemNguyxn Altium Library.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\nemNguyxn Altium Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9288EE17-9EF0-4179-8052-90AAD434EF15}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F796381-8072-455F-9A07-31DD4ADB0130}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="792" activeTab="2" xr2:uid="{48E472BD-29E7-4696-BAF4-9A71FEFB4210}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="792" activeTab="1" xr2:uid="{48E472BD-29E7-4696-BAF4-9A71FEFB4210}"/>
   </bookViews>
   <sheets>
     <sheet name="Capacitors - MLCC" sheetId="1" r:id="rId1"/>
     <sheet name="Capacitors - TANT" sheetId="6" r:id="rId2"/>
     <sheet name="Capacitors - ALU" sheetId="7" r:id="rId3"/>
     <sheet name="Connectors" sheetId="4" r:id="rId4"/>
-    <sheet name="Resistors" sheetId="2" r:id="rId5"/>
-    <sheet name="Inductors" sheetId="3" r:id="rId6"/>
+    <sheet name="Inductors" sheetId="3" r:id="rId5"/>
+    <sheet name="Resistors" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="12">
   <si>
     <t>DatabaseID</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>Footprint Ref</t>
+  </si>
+  <si>
+    <t>Power</t>
   </si>
 </sst>
 </file>
@@ -211,7 +214,231 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="48">
+  <dxfs count="64">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <protection locked="0" hidden="0"/>
@@ -426,8 +653,38 @@
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <protection locked="0" hidden="0"/>
+      <border>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -639,8 +896,38 @@
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <protection locked="0" hidden="0"/>
+      <border>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -854,92 +1141,51 @@
     <dxf>
       <border>
         <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <border>
         <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="0" hidden="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -955,60 +1201,80 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E978C71F-A41E-43CE-A220-B2050F36ACBD}" name="Table2" displayName="Table2" ref="A1:K1048576" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26" headerRowBorderDxfId="46" tableBorderDxfId="47" totalsRowBorderDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E978C71F-A41E-43CE-A220-B2050F36ACBD}" name="Table2" displayName="Table2" ref="A1:K1048576" totalsRowShown="0" headerRowDxfId="63" dataDxfId="61" headerRowBorderDxfId="62" tableBorderDxfId="60" totalsRowBorderDxfId="59">
   <autoFilter ref="A1:K1048576" xr:uid="{66998175-B102-4776-A50E-F63953463B9A}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{D053E276-1DC1-410A-89A7-0A308FA395E7}" name="DatabaseID" dataDxfId="38"/>
-    <tableColumn id="2" xr3:uid="{3D0743B8-4ED9-4DD5-90BD-9A5D36CF1E57}" name="Part Number" dataDxfId="37"/>
-    <tableColumn id="3" xr3:uid="{44837010-7A95-4B7A-AC92-B1AEDFDB4395}" name="Manufacturer" dataDxfId="36"/>
-    <tableColumn id="4" xr3:uid="{9A8473E6-0608-4B08-9C01-31AA1D97045A}" name="Description" dataDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{EF657F5B-B649-4F0E-B341-F87792D4634F}" name="Type" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{63B397D1-B9AF-4728-9D7C-B26B5936532F}" name="Value" dataDxfId="33"/>
-    <tableColumn id="7" xr3:uid="{DBA5C301-A0C3-4AB9-B38F-2528D982DD51}" name="Tolerance" dataDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{662E95A4-09C3-4BFB-A037-8AB764D38C92}" name="Voltage Rating" dataDxfId="31"/>
-    <tableColumn id="9" xr3:uid="{E1FADA70-2281-4E8C-AD98-7321030D7867}" name="Package" dataDxfId="30"/>
-    <tableColumn id="10" xr3:uid="{E422F18C-9AAE-4FFC-8AD1-55847642433D}" name="Library Ref" dataDxfId="29"/>
-    <tableColumn id="11" xr3:uid="{05751D01-7852-4B71-8680-0E34D82D6809}" name="Footprint Ref" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{D053E276-1DC1-410A-89A7-0A308FA395E7}" name="DatabaseID" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{3D0743B8-4ED9-4DD5-90BD-9A5D36CF1E57}" name="Part Number" dataDxfId="57"/>
+    <tableColumn id="3" xr3:uid="{44837010-7A95-4B7A-AC92-B1AEDFDB4395}" name="Manufacturer" dataDxfId="56"/>
+    <tableColumn id="4" xr3:uid="{9A8473E6-0608-4B08-9C01-31AA1D97045A}" name="Description" dataDxfId="55"/>
+    <tableColumn id="5" xr3:uid="{EF657F5B-B649-4F0E-B341-F87792D4634F}" name="Type" dataDxfId="54"/>
+    <tableColumn id="6" xr3:uid="{63B397D1-B9AF-4728-9D7C-B26B5936532F}" name="Value" dataDxfId="53"/>
+    <tableColumn id="7" xr3:uid="{DBA5C301-A0C3-4AB9-B38F-2528D982DD51}" name="Tolerance" dataDxfId="52"/>
+    <tableColumn id="8" xr3:uid="{662E95A4-09C3-4BFB-A037-8AB764D38C92}" name="Voltage Rating" dataDxfId="51"/>
+    <tableColumn id="9" xr3:uid="{E1FADA70-2281-4E8C-AD98-7321030D7867}" name="Package" dataDxfId="50"/>
+    <tableColumn id="10" xr3:uid="{E422F18C-9AAE-4FFC-8AD1-55847642433D}" name="Library Ref" dataDxfId="49"/>
+    <tableColumn id="11" xr3:uid="{05751D01-7852-4B71-8680-0E34D82D6809}" name="Footprint Ref" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{613EA8BF-6FD5-4826-94E3-6C0A015B46ED}" name="Table24" displayName="Table24" ref="A1:K1048576" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" headerRowBorderDxfId="43" tableBorderDxfId="44" totalsRowBorderDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{613EA8BF-6FD5-4826-94E3-6C0A015B46ED}" name="Table24" displayName="Table24" ref="A1:K1048576" totalsRowShown="0" headerRowDxfId="47" dataDxfId="45" headerRowBorderDxfId="46" tableBorderDxfId="44" totalsRowBorderDxfId="43">
   <autoFilter ref="A1:K1048576" xr:uid="{66998175-B102-4776-A50E-F63953463B9A}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{ABAD5B74-FBBF-4037-88B1-46B590217F8C}" name="DatabaseID" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{B357D2EB-5D65-4E54-8A2B-E575E5800D90}" name="Part Number" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{3037DE1D-4ED1-4709-B134-407F859F9709}" name="Manufacturer" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{6D5344AF-E9E5-4873-A6B9-AD21BFD38674}" name="Description" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{92396102-04A0-484E-8F33-D82E15D7FEB3}" name="Type" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{041BA87B-9138-4EEF-9E60-F8785194984B}" name="Value" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{D14B40F2-7BEE-43AB-9D7A-96001B6E8891}" name="Tolerance" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{E9C8F92E-1AB1-4BBF-8BDC-82C467938516}" name="Voltage Rating" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{78550022-E67D-4FA4-AE8C-0AE24BC02009}" name="Package" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{88338EC5-E16E-4603-85E4-C6BAC0B393D3}" name="Library Ref" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{74DA26E8-9EBA-4054-B48F-A6FA2F23581E}" name="Footprint Ref" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{ABAD5B74-FBBF-4037-88B1-46B590217F8C}" name="DatabaseID" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{B357D2EB-5D65-4E54-8A2B-E575E5800D90}" name="Part Number" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{3037DE1D-4ED1-4709-B134-407F859F9709}" name="Manufacturer" dataDxfId="40"/>
+    <tableColumn id="4" xr3:uid="{6D5344AF-E9E5-4873-A6B9-AD21BFD38674}" name="Description" dataDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{92396102-04A0-484E-8F33-D82E15D7FEB3}" name="Type" dataDxfId="38"/>
+    <tableColumn id="6" xr3:uid="{041BA87B-9138-4EEF-9E60-F8785194984B}" name="Value" dataDxfId="37"/>
+    <tableColumn id="7" xr3:uid="{D14B40F2-7BEE-43AB-9D7A-96001B6E8891}" name="Tolerance" dataDxfId="36"/>
+    <tableColumn id="8" xr3:uid="{E9C8F92E-1AB1-4BBF-8BDC-82C467938516}" name="Voltage Rating" dataDxfId="35"/>
+    <tableColumn id="9" xr3:uid="{78550022-E67D-4FA4-AE8C-0AE24BC02009}" name="Package" dataDxfId="34"/>
+    <tableColumn id="10" xr3:uid="{88338EC5-E16E-4603-85E4-C6BAC0B393D3}" name="Library Ref" dataDxfId="33"/>
+    <tableColumn id="11" xr3:uid="{74DA26E8-9EBA-4054-B48F-A6FA2F23581E}" name="Footprint Ref" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{958776BD-29AD-40C3-AF4E-7B69DC8A8480}" name="Table245" displayName="Table245" ref="A1:K1048576" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="40" tableBorderDxfId="41" totalsRowBorderDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{958776BD-29AD-40C3-AF4E-7B69DC8A8480}" name="Table245" displayName="Table245" ref="A1:K1048576" totalsRowShown="0" headerRowDxfId="31" dataDxfId="29" headerRowBorderDxfId="30" tableBorderDxfId="28" totalsRowBorderDxfId="27">
   <autoFilter ref="A1:K1048576" xr:uid="{66998175-B102-4776-A50E-F63953463B9A}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{578EF4B6-1205-400A-AB04-BCC621817317}" name="DatabaseID" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{C03DC7B0-7FDB-4F9E-82FA-5B3B586BC44D}" name="Part Number" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{FE154028-2653-4796-A792-FF59166BD7B5}" name="Manufacturer" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{B0EF08C2-19D4-4ABF-85D3-776528F97E7B}" name="Description" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{650416EB-DF25-4AFA-9167-F1BEEE0E2ED1}" name="Type" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{390CB8A7-5EBB-48C9-8F91-40F6028729C0}" name="Value" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{AB722699-5B86-4B84-B4A0-C1E9991BF7AA}" name="Tolerance" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{5AF4F9CC-95C5-4951-A11B-4C55400E4486}" name="Voltage Rating" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{46E371D3-ED90-4CBF-8B90-D8EF019119FD}" name="Package" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{FE782A35-5F6B-4781-A345-33D3D7F66887}" name="Library Ref" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{07C3FA81-E9DD-4BF5-95C8-98467E814AC5}" name="Footprint Ref" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{578EF4B6-1205-400A-AB04-BCC621817317}" name="DatabaseID" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{C03DC7B0-7FDB-4F9E-82FA-5B3B586BC44D}" name="Part Number" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{FE154028-2653-4796-A792-FF59166BD7B5}" name="Manufacturer" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{B0EF08C2-19D4-4ABF-85D3-776528F97E7B}" name="Description" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{650416EB-DF25-4AFA-9167-F1BEEE0E2ED1}" name="Type" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{390CB8A7-5EBB-48C9-8F91-40F6028729C0}" name="Value" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{AB722699-5B86-4B84-B4A0-C1E9991BF7AA}" name="Tolerance" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{5AF4F9CC-95C5-4951-A11B-4C55400E4486}" name="Voltage Rating" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{46E371D3-ED90-4CBF-8B90-D8EF019119FD}" name="Package" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{FE782A35-5F6B-4781-A345-33D3D7F66887}" name="Library Ref" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{07C3FA81-E9DD-4BF5-95C8-98467E814AC5}" name="Footprint Ref" dataDxfId="16"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{56DFE9D7-A586-4A0E-A2CA-A36F6B88FD21}" name="Table22" displayName="Table22" ref="A1:K1048576" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14" headerRowBorderDxfId="12" tableBorderDxfId="13" totalsRowBorderDxfId="11">
+  <autoFilter ref="A1:K1048576" xr:uid="{66998175-B102-4776-A50E-F63953463B9A}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{383F46C5-6D9A-4458-AB09-2334CA05B166}" name="DatabaseID" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{E1D0938F-34D6-4CDF-9CF1-09127C5FB81D}" name="Part Number" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{E3EE402E-6851-4F30-A68D-FFE41DEE8734}" name="Manufacturer" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{F58A2E50-B90F-4B75-B2F1-62A41B36E8A2}" name="Description" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{57FF66B9-D150-40CB-A447-18046EBD8484}" name="Type" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{15054A02-48FD-4D7B-BCF6-27A6AE132F11}" name="Value" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{ACF71B3D-B981-4103-AE6B-C2C78C0FF5C6}" name="Tolerance" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{44CD9A7C-8ABD-41EA-87C8-23AB3C580572}" name="Power" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{97EB146F-258E-4DB4-9827-85C4D5496FEE}" name="Package" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{5A50C510-A62B-4496-9062-CC110657206B}" name="Library Ref" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{B679DF6A-A84C-4C29-B7BD-114985868074}" name="Footprint Ref" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1494,8 +1760,8 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{636BF1F5-4643-44AA-8DF3-C9A428559F7E}">
-  <sheetPr codeName="Sheet4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8757DF19-A5AC-4F46-B626-CB1B3F0DFD6C}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1504,11 +1770,58 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8757DF19-A5AC-4F46-B626-CB1B3F0DFD6C}">
-  <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63DBFBEF-E64B-4FE9-98AA-053F582456D6}">
+  <dimension ref="A1:K1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="14.140625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="74.140625" style="3" customWidth="1"/>
+    <col min="5" max="10" width="18.5703125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" style="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>